--- a/438889381_feed_kedr_uray.xlsx
+++ b/438889381_feed_kedr_uray.xlsx
@@ -2207,7 +2207,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/kedr-uray-samovyvoz_2026-07-16/8742178634/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/kedr-uray-samovyvoz_2026-07-16/8742178634/01_02.jpg</t>
+          <t>https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/kedr-uray-samovyvoz_2026-07-15/8742178634/01_01.jpg | https://raw.githubusercontent.com/Harmageddon14/avito-feeds/main/img/438889381/kedr-uray-samovyvoz_2026-07-15/8742178634/01_02.jpg</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>2026-07-16T08:00:00+03:00</t>
+          <t>2026-07-15T13:40:00+03:00</t>
         </is>
       </c>
     </row>
